--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10659,7 +10659,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -16449,7 +16449,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20304,7 +20304,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21468,7 +21468,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23010,7 +23010,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24552,7 +24552,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26865,7 +26865,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28407,7 +28407,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29949,7 +29949,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -31113,7 +31113,7 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN159" t="b">
@@ -31884,7 +31884,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33426,7 +33426,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34197,7 +34197,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34968,7 +34968,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35739,7 +35739,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36510,7 +36510,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37281,7 +37281,7 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -38823,7 +38823,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -39594,7 +39594,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -40758,7 +40758,7 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN209" t="b">
@@ -41529,7 +41529,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -43071,7 +43071,7 @@
       </c>
       <c r="AM221" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN221" t="b">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44613,7 +44613,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46155,7 +46155,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -46926,7 +46926,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47697,7 +47697,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48468,7 +48468,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN249" t="b">

--- a/diseases/d054/2000-2004.xlsx
+++ b/diseases/d054/2000-2004.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9107,7 +9107,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11813,7 +11813,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13355,7 +13355,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15668,7 +15668,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16439,7 +16439,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19523,7 +19523,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21458,7 +21458,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22229,7 +22229,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26084,7 +26084,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26855,7 +26855,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29168,7 +29168,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29939,7 +29939,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31874,7 +31874,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32645,7 +32645,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33416,7 +33416,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34187,7 +34187,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -34958,7 +34958,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35729,7 +35729,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -36500,7 +36500,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -38042,7 +38042,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -38813,7 +38813,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -39584,7 +39584,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41519,7 +41519,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -42290,7 +42290,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -43061,7 +43061,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -43832,7 +43832,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45374,7 +45374,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46145,7 +46145,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -46916,7 +46916,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47687,7 +47687,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48458,7 +48458,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
